--- a/data/trans_orig/P21D_3_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D_3_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos en 2023</t>
+          <t>Población que, necesitando medicamentos, no los pudo comprar por motivos económicos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223163</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216624</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>441364</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1073,97 +1073,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179877</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>176766</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1416,97 +1416,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4193</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1165</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>2973</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>411003</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77787</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>491174</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415196</t>
+          <t>415195</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1759,97 +1759,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1765</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3507</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3835</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3983</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3485</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>454244</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335487</t>
+          <t>335815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>791846</t>
+          <t>791348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4665</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>539</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>411932</t>
+          <t>412007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>632866</t>
+          <t>632748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>638156</t>
+          <t>638158</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2445,97 +2445,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4140</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1259</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1566</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>119187</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317497</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>440518</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>3682</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>540</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5686</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>746</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6589</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1618726</t>
+          <t>1619552</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1543929</t>
+          <t>1543711</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1549074</t>
+          <t>1549075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3166261</t>
+          <t>3165778</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3172142</t>
+          <t>3172104</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">

--- a/data/trans_orig/P21D_3_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P21D_3_R-Clase-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>244410</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>217952</t>
+          <t>234824</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>442891</t>
+          <t>479234</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>181664</t>
+          <t>196927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178036</t>
+          <t>196622</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>359699</t>
+          <t>393549</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1594,7 +1594,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>415195</t>
+          <t>188837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>78952</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>494147</t>
+          <t>275458</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>338635</t>
+          <t>386560</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335815</t>
+          <t>382869</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>794644</t>
+          <t>898395</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>791348</t>
+          <t>895572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>456009</t>
+          <t>511835</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>339322</t>
+          <t>387262</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>795331</t>
+          <t>899097</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2107,57 +2107,57 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1311</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4713</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4590</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,22 +2167,22 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5949</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -2210,69 +2210,69 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>221336</t>
+          <t>265260</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>218475</t>
+          <t>261552</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
+          <t>99,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>387812</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>384410</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>389123</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,79%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>415271</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>412007</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>416597</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,68%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>826</t>
@@ -2280,27 +2280,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>636606</t>
+          <t>653073</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>632748</t>
+          <t>649937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>638158</t>
+          <t>654575</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>222100</t>
+          <t>266007</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>416597</t>
+          <t>389123</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>638697</t>
+          <t>655130</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>638697</t>
+          <t>655130</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>638697</t>
+          <t>655130</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123327</t>
+          <t>117437</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>318756</t>
+          <t>355223</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>442084</t>
+          <t>472660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,17 +2823,17 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5631</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -2896,17 +2896,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1622470</t>
+          <t>1524707</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1619552</t>
+          <t>1521481</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2931,27 +2931,27 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1547602</t>
+          <t>1647662</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1543711</t>
+          <t>1644044</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1549075</t>
+          <t>1649108</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2966,17 +2966,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3170072</t>
+          <t>3172370</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3165778</t>
+          <t>3168499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3172104</t>
+          <t>3174421</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1623234</t>
+          <t>1525454</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1549615</t>
+          <t>1649675</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1549615</t>
+          <t>1649675</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1549615</t>
+          <t>1649675</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>3172850</t>
+          <t>3175129</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3172850</t>
+          <t>3175129</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3172850</t>
+          <t>3175129</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
